--- a/xls/square_eigen_28_quad4_26.xlsx
+++ b/xls/square_eigen_28_quad4_26.xlsx
@@ -75,139 +75,139 @@
     <t>0.14764865258307533</t>
   </si>
   <si>
-    <t>1.5148315860029543e-5</t>
+    <t>5.015667131046522e-5</t>
   </si>
   <si>
     <t>0.117060084723833</t>
   </si>
   <si>
-    <t>1.5085313034350105e-5</t>
+    <t>5.4680075720689435e-5</t>
   </si>
   <si>
     <t>0.09327478067839785</t>
   </si>
   <si>
-    <t>1.5371955603441598e-5</t>
+    <t>4.7732023235178995e-5</t>
   </si>
   <si>
     <t>0.015407481956186775</t>
   </si>
   <si>
-    <t>1.495180909559026e-5</t>
+    <t>4.9611898807492155e-5</t>
   </si>
   <si>
     <t>0.003988593090988146</t>
   </si>
   <si>
-    <t>1.537869032036232e-5</t>
+    <t>4.7898930687678144e-5</t>
   </si>
   <si>
     <t>0.02357661337341179</t>
   </si>
   <si>
-    <t>1.5089356294289097e-5</t>
+    <t>4.872306095787502e-5</t>
   </si>
   <si>
     <t>0.002894417140209158</t>
   </si>
   <si>
-    <t>1.5011016801567262e-5</t>
+    <t>5.8636071700137796e-5</t>
   </si>
   <si>
     <t>0.00031635271157244246</t>
   </si>
   <si>
-    <t>1.5055911606099724e-5</t>
+    <t>41.95603240660888</t>
   </si>
   <si>
     <t>2.0774142439100985e-5</t>
   </si>
   <si>
-    <t>1.9129534128244143e-5</t>
+    <t>38.55002167001232</t>
   </si>
   <si>
     <t>1.649247116413413e-5</t>
   </si>
   <si>
-    <t>1.9633356143382563e-5</t>
+    <t>36.135700750676435</t>
   </si>
   <si>
     <t>3.326104504030258e-5</t>
   </si>
   <si>
-    <t>1.5062992236596497e-5</t>
+    <t>32.85120712083145</t>
   </si>
   <si>
     <t>0.00011668298332037577</t>
   </si>
   <si>
-    <t>1.5092683730751652e-5</t>
+    <t>30.29603894592275</t>
   </si>
   <si>
     <t>0.00023786325423505155</t>
   </si>
   <si>
-    <t>1.5209510110013967e-5</t>
+    <t>27.776332343791307</t>
   </si>
   <si>
     <t>0.0004116900481023551</t>
   </si>
   <si>
-    <t>1.490428463872297e-5</t>
+    <t>25.201295446935358</t>
   </si>
   <si>
     <t>0.0009950073218800235</t>
   </si>
   <si>
-    <t>1.492022969961276e-5</t>
+    <t>22.62660208997273</t>
   </si>
   <si>
     <t>0.0009734598660146059</t>
   </si>
   <si>
-    <t>1.5060965355704816e-5</t>
+    <t>19.15725530133954</t>
   </si>
   <si>
     <t>4.19065445191342e-5</t>
   </si>
   <si>
-    <t>1.492026897435695e-5</t>
+    <t>14.207120514784878</t>
   </si>
   <si>
     <t>3.0469002369544023</t>
   </si>
   <si>
-    <t>7.859404967031326</t>
+    <t>7.784967687718123</t>
   </si>
   <si>
     <t>3.047398849125165</t>
   </si>
   <si>
-    <t>20.757869038373222</t>
+    <t>20.71089540108433</t>
   </si>
   <si>
     <t>3.047611388699264</t>
   </si>
   <si>
-    <t>0.0001449891677791843</t>
+    <t>0.00017962449959700984</t>
   </si>
   <si>
     <t>3.047802783419764</t>
   </si>
   <si>
-    <t>0.0002448617098660898</t>
+    <t>0.0009897146554846865</t>
   </si>
   <si>
     <t>3.047976625001217</t>
   </si>
   <si>
-    <t>0.00010381571007779236</t>
+    <t>0.00013643501902078995</t>
   </si>
   <si>
     <t>3.048134383405516</t>
   </si>
   <si>
-    <t>9.233859224184306e-5</t>
+    <t>4.824755692952131e-5</t>
   </si>
 </sst>
 </file>
@@ -635,7 +635,7 @@
         <v>-0.8307705119796701</v>
       </c>
       <c r="L10">
-        <v>-4.819635647911013</v>
+        <v>-4.2996712935383075</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -673,7 +673,7 @@
         <v>-0.9315911658951695</v>
       </c>
       <c r="L11">
-        <v>-4.821445673378927</v>
+        <v>-4.2621708926950195</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -711,7 +711,7 @@
         <v>-1.030235763464014</v>
       </c>
       <c r="L12">
-        <v>-4.813270878514752</v>
+        <v>-4.321190156640437</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -749,7 +749,7 @@
         <v>-1.8122683322023887</v>
       </c>
       <c r="L13">
-        <v>-4.825306256657382</v>
+        <v>-4.304414150794192</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -787,7 +787,7 @@
         <v>-2.399180267363367</v>
       </c>
       <c r="L14">
-        <v>-4.813080648335531</v>
+        <v>-4.31967418181768</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -825,7 +825,7 @@
         <v>-1.6275185783278419</v>
       </c>
       <c r="L15">
-        <v>-4.821329286652578</v>
+        <v>-4.312265435577232</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -863,7 +863,7 @@
         <v>-2.5384388786641208</v>
       </c>
       <c r="L16">
-        <v>-4.823589888945706</v>
+        <v>-4.2318351327751795</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -901,7 +901,7 @@
         <v>-3.4998284386952636</v>
       </c>
       <c r="L17">
-        <v>-4.822292943670791</v>
+        <v>1.622794412186279</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -939,7 +939,7 @@
         <v>-4.682476894939919</v>
       </c>
       <c r="L18">
-        <v>-4.718295606449259</v>
+        <v>1.586024626515747</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -977,7 +977,7 @@
         <v>-4.782714266578623</v>
       </c>
       <c r="L19">
-        <v>-4.707005455368583</v>
+        <v>1.5579364810604204</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -1015,7 +1015,7 @@
         <v>-4.4780641096532765</v>
       </c>
       <c r="L20">
-        <v>-4.822088747739501</v>
+        <v>1.516551332382382</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -1053,7 +1053,7 @@
         <v>-3.932992475479226</v>
       </c>
       <c r="L21">
-        <v>-4.821233528559405</v>
+        <v>1.481385850403913</v>
       </c>
     </row>
     <row r="22" spans="1:12">
@@ -1091,7 +1091,7 @@
         <v>-3.623672643778379</v>
       </c>
       <c r="L22">
-        <v>-4.817884774109002</v>
+        <v>1.4436748998605673</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -1129,7 +1129,7 @@
         <v>-3.3854296311965153</v>
       </c>
       <c r="L23">
-        <v>-4.826688863972904</v>
+        <v>1.40142286582104</v>
       </c>
     </row>
     <row r="24" spans="1:12">
@@ -1167,7 +1167,7 @@
         <v>-3.0021737234347854</v>
       </c>
       <c r="L24">
-        <v>-4.826224490770426</v>
+        <v>1.3546193394441612</v>
       </c>
     </row>
     <row r="25" spans="1:12">
@@ -1205,7 +1205,7 @@
         <v>-3.0116819489489743</v>
       </c>
       <c r="L25">
-        <v>-4.822147190471361</v>
+        <v>1.282333286951852</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -1243,7 +1243,7 @@
         <v>-4.377718148236592</v>
       </c>
       <c r="L26">
-        <v>-4.826223347572059</v>
+        <v>1.152506064467888</v>
       </c>
     </row>
     <row r="27" spans="1:12">
@@ -1281,7 +1281,7 @@
         <v>0.48385823458056587</v>
       </c>
       <c r="L27">
-        <v>0.89538966699144</v>
+        <v>0.8912568143254828</v>
       </c>
     </row>
     <row r="28" spans="1:12">
@@ -1319,7 +1319,7 @@
         <v>0.48392929919744687</v>
       </c>
       <c r="L28">
-        <v>1.3171827676553594</v>
+        <v>1.3161988752982747</v>
       </c>
     </row>
     <row r="29" spans="1:12">
@@ -1357,7 +1357,7 @@
         <v>0.4839595878304936</v>
       </c>
       <c r="L29">
-        <v>-3.838664442933686</v>
+        <v>-3.7456344287258325</v>
       </c>
     </row>
     <row r="30" spans="1:12">
@@ -1395,7 +1395,7 @@
         <v>0.4839868613409258</v>
       </c>
       <c r="L30">
-        <v>-3.611079122159859</v>
+        <v>-3.004489998746811</v>
       </c>
     </row>
     <row r="31" spans="1:12">
@@ -1433,7 +1433,7 @@
         <v>0.48401163206654174</v>
       </c>
       <c r="L31">
-        <v>-3.9837369212097777</v>
+        <v>-3.8650741442285237</v>
       </c>
     </row>
     <row r="32" spans="1:12">
@@ -1471,7 +1471,7 @@
         <v>0.48403410987391166</v>
       </c>
       <c r="L32">
-        <v>-4.034616750818664</v>
+        <v>-4.316524672763507</v>
       </c>
     </row>
   </sheetData>
